--- a/output/pdf_financials_xlsx/RGEN.xlsx
+++ b/output/pdf_financials_xlsx/RGEN.xlsx
@@ -480,11 +480,15 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.057865</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.064985</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -498,11 +502,15 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>-0.003217</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-0.003054</v>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -729,10 +737,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>0.057865</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>0.064985</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -985,10 +993,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.821449</v>
+        <v>-2.879314</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-2.815042</v>
+        <v>-2.880027</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0.105811</v>
@@ -1017,10 +1025,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-2.821449</v>
+        <v>-2.879314</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-2.815042</v>
+        <v>-2.880027</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0.105811</v>
@@ -1033,10 +1041,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-7410.240315167433</v>
+        <v>-7562.21667760998</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-6168.062402769561</v>
+        <v>-6310.451587458095</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>121.7561907392065</v>
@@ -1213,20 +1221,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0.283382</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.034381</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.132365</v>
       </c>
     </row>
     <row r="47">
@@ -1257,20 +1259,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.283382</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.034381</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.132365</v>
       </c>
     </row>
     <row r="49">
@@ -1518,13 +1514,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0.422977</v>
+        <v>0.139595</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1.265078</v>
+        <v>1.230697</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.2696</v>
+        <v>0.137235</v>
       </c>
     </row>
     <row r="61">
@@ -2959,13 +2955,13 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>0</v>
+        <v>-0.051477</v>
       </c>
       <c r="C139" s="3" t="n">
-        <v>0</v>
+        <v>-0.051659</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0</v>
+        <v>-0.010938</v>
       </c>
     </row>
     <row r="140">
@@ -2975,13 +2971,13 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>0</v>
+        <v>-0.051477</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0</v>
+        <v>-0.051659</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>0</v>
+        <v>-0.010938</v>
       </c>
     </row>
     <row r="141">
@@ -3254,7 +3250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -6282,7 +6278,11 @@
           <t>Lease payment 13</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -6801,7 +6801,11 @@
           <t>Lease payment 14</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>-0.051477</v>
       </c>
@@ -7996,7 +8000,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
@@ -8029,7 +8033,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">

--- a/output/pdf_financials_xlsx/RGEN.xlsx
+++ b/output/pdf_financials_xlsx/RGEN.xlsx
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-2.821449</v>
+        <v>-1.164166</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.815042</v>
+        <v>-0.927385</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.105811</v>
+        <v>-1.337359</v>
       </c>
     </row>
     <row r="27">
@@ -5715,7 +5715,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -6249,7 +6253,11 @@
           <t>Proceeds from private placement 15</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -6772,7 +6780,11 @@
           <t>Private placement 16</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>0.425</v>
       </c>
@@ -7601,7 +7613,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -8225,7 +8241,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
         <v>-1.164166</v>
       </c>
